--- a/CMSLoginCreds.xlsx
+++ b/CMSLoginCreds.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="8715"/>
+    <workbookView windowWidth="30240" windowHeight="13680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="56">
   <si>
     <t>id</t>
   </si>
@@ -202,10 +202,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -720,19 +720,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1448,15 +1448,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="9.14285714285714" style="1"/>
-    <col min="2" max="2" width="20.3142857142857" style="2" customWidth="1"/>
-    <col min="3" max="3" width="23.1428571428571" style="2" customWidth="1"/>
-    <col min="4" max="4" width="21.8571428571429" style="2" customWidth="1"/>
-    <col min="5" max="5" width="19.4285714285714" style="2" customWidth="1"/>
-    <col min="6" max="6" width="29.4285714285714" style="2" customWidth="1"/>
-    <col min="7" max="7" width="47.2857142857143" style="2" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="20.3125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="21.859375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="19.4296875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="29.4296875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="47.2890625" style="2" customWidth="1"/>
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1512,7 +1512,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" ht="17" spans="1:8">
       <c r="A3" s="5" t="s">
         <v>15</v>
       </c>
@@ -1529,12 +1529,14 @@
       <c r="F3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="6"/>
+      <c r="G3" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="H3" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" ht="17" spans="1:8">
       <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
@@ -1551,12 +1553,14 @@
       <c r="F4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="6"/>
+      <c r="G4" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="H4" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" ht="17" spans="1:8">
       <c r="A5" s="5" t="s">
         <v>23</v>
       </c>
@@ -1580,7 +1584,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" ht="17" spans="1:8">
       <c r="A6" s="5" t="s">
         <v>28</v>
       </c>
@@ -1606,7 +1610,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" ht="17" spans="1:8">
       <c r="A7" s="5" t="s">
         <v>30</v>
       </c>
@@ -1632,7 +1636,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" ht="17" spans="1:8">
       <c r="A8" s="5" t="s">
         <v>35</v>
       </c>
@@ -1654,7 +1658,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" ht="17" spans="1:8">
       <c r="A9" s="5" t="s">
         <v>37</v>
       </c>
@@ -1678,7 +1682,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" ht="17" spans="1:8">
       <c r="A10" s="5" t="s">
         <v>41</v>
       </c>
@@ -1700,7 +1704,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" ht="17" spans="1:8">
       <c r="A11" s="5" t="s">
         <v>45</v>
       </c>
@@ -1722,7 +1726,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" ht="17" spans="1:8">
       <c r="A12" s="5" t="s">
         <v>47</v>
       </c>
@@ -1744,7 +1748,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" ht="17" spans="1:8">
       <c r="A13" s="5" t="s">
         <v>50</v>
       </c>
@@ -1766,7 +1770,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" ht="17" spans="1:8">
       <c r="A14" s="5" t="s">
         <v>54</v>
       </c>
@@ -1795,7 +1799,6 @@
     <hyperlink ref="D5" r:id="rId3" display="User@12345" tooltip="mailto:User@12345"/>
     <hyperlink ref="G7" r:id="rId4" display="https://wafcms-isl-stg.sportz.io/login/login?refval=/"/>
     <hyperlink ref="G6" r:id="rId5" display="https://beta-wafcms.sportz.io/login/login?refval" tooltip="https://beta-wafcms.sportz.io/login/login?refval"/>
-    <hyperlink ref="G2" r:id="rId5" display="https://beta-wafcms.sportz.io/login/login?refval" tooltip="https://beta-wafcms.sportz.io/login/login?refval"/>
     <hyperlink ref="G5" r:id="rId5" display="https://beta-wafcms.sportz.io/login/login?refval" tooltip="https://beta-wafcms.sportz.io/login/login?refval"/>
     <hyperlink ref="D9" r:id="rId6" display="Download@1234"/>
     <hyperlink ref="G9" r:id="rId5" display="https://beta-wafcms.sportz.io/login/login?refval" tooltip="https://beta-wafcms.sportz.io/login/login?refval"/>
@@ -1808,6 +1811,9 @@
     <hyperlink ref="D13" r:id="rId10" display="Delete@1234"/>
     <hyperlink ref="G13" r:id="rId5" display="https://beta-wafcms.sportz.io/login/login?refval" tooltip="https://beta-wafcms.sportz.io/login/login?refval"/>
     <hyperlink ref="G14" r:id="rId5" display="https://beta-wafcms.sportz.io/login/login?refval" tooltip="https://beta-wafcms.sportz.io/login/login?refval"/>
+    <hyperlink ref="G2" r:id="rId5" display="https://beta-wafcms.sportz.io/login/login?refval" tooltip="https://beta-wafcms.sportz.io/login/login?refval"/>
+    <hyperlink ref="G3" r:id="rId5" display="https://beta-wafcms.sportz.io/login/login?refval" tooltip="https://beta-wafcms.sportz.io/login/login?refval"/>
+    <hyperlink ref="G4" r:id="rId5" display="https://beta-wafcms.sportz.io/login/login?refval" tooltip="https://beta-wafcms.sportz.io/login/login?refval"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
